--- a/O.F China lane Analysis.xlsx
+++ b/O.F China lane Analysis.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/thuhuong_ngo_nykgroup_com/Documents/Streamlit_Starter_Kit_CS_HAD/2026 bidding preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{3F479565-A40F-41CD-8273-DAD36C479CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AC7104-3B2D-4A57-A2F8-48A46E63FEF0}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{3F479565-A40F-41CD-8273-DAD36C479CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DE00E3-5877-4015-BFA1-7898D73475B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{110F69CB-7609-4F85-B310-6E083916393A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
+    <sheet name="OF" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="\0">#REF!</definedName>
     <definedName name="\a">#REF!</definedName>
@@ -985,6 +982,7 @@
     <definedName name="_f5" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="_FES250">#REF!</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">OF!$A$1:$Q$31</definedName>
     <definedName name="_fullfill" hidden="1">#REF!</definedName>
     <definedName name="_Goi8" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="_gon4">#REF!</definedName>
@@ -15749,54 +15747,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>NGO THI THU HUONG</author>
-  </authors>
-  <commentList>
-    <comment ref="V14" authorId="0" shapeId="0" xr:uid="{9DCAEAC0-FDC5-4ABA-8514-913CFB05FB25}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NGO THI THU HUONG:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-YLVN share 50/50 phần chênh lệch 200$ vs KVP</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="42">
-  <si>
-    <t>CNSHA</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>P&amp;L</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="31">
   <si>
     <t>Carrier</t>
   </si>
@@ -15804,55 +15756,19 @@
     <t>ETD</t>
   </si>
   <si>
-    <t>20'</t>
-  </si>
-  <si>
-    <t>40'</t>
-  </si>
-  <si>
     <t>OF BR 20'</t>
-  </si>
-  <si>
-    <t>BR LSS 20'</t>
-  </si>
-  <si>
-    <t>LSS 40'</t>
   </si>
   <si>
     <t>Total BR surcharge 20'</t>
   </si>
   <si>
-    <t>BAF 20'</t>
-  </si>
-  <si>
-    <t>BAF 40'</t>
-  </si>
-  <si>
-    <t>PSS 20'</t>
-  </si>
-  <si>
-    <t>PSS 40'</t>
-  </si>
-  <si>
     <t>Total SR Surcharge 20'</t>
-  </si>
-  <si>
-    <t>Total Surcharge 40'</t>
   </si>
   <si>
     <t>Total SR 20'</t>
   </si>
   <si>
-    <t>Total 40'</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>SITC</t>
-  </si>
-  <si>
-    <t>Inc.</t>
   </si>
   <si>
     <t>SITC/VTX7</t>
@@ -15911,34 +15827,34 @@
   <si>
     <t>P&amp;L 40'</t>
   </si>
+  <si>
+    <t>Vol. 20'</t>
+  </si>
+  <si>
+    <t>Vol. 40'</t>
+  </si>
+  <si>
+    <t>Total P&amp;L 20'</t>
+  </si>
+  <si>
+    <t>Total P&amp;L 40'</t>
+  </si>
+  <si>
+    <t>Total P&amp;L</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -15964,60 +15880,17 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -16032,25 +15905,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -16068,172 +15928,55 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{549623E2-9112-4C42-AA48-036BE46EB6C0}"/>
+    <cellStyle name="Normal 10" xfId="1" xr:uid="{549623E2-9112-4C42-AA48-036BE46EB6C0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -16246,43 +15989,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="O.F China lane Analysis"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="O.F Korea lane"/>
-      <sheetName val="O.F Korea lane(old)"/>
-      <sheetName val="O.F China lane1"/>
-      <sheetName val="O.F China lane"/>
-      <sheetName val="analysis"/>
-      <sheetName val="xmn"/>
-      <sheetName val="SFP instruction"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="MNL-HAN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16601,8 +16307,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9799209-B45B-4B19-8CB2-D7010CEA28CB}">
-  <dimension ref="A1:AD50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9799209-B45B-4B19-8CB2-D7010CEA28CB}">
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
@@ -16615,2211 +16321,1506 @@
     <col min="25" max="25" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="2"/>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46024</v>
+      </c>
+      <c r="D2" s="5">
+        <v>265</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="8">
+        <v>105</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8">
+        <v>370</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8">
+        <v>400</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8">
+        <v>0</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8">
+        <v>400</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46055</v>
+      </c>
+      <c r="D3" s="3">
+        <v>175</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8">
+        <v>175</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8">
+        <v>400</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8">
+        <v>400</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8">
+        <v>225</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46084</v>
+      </c>
+      <c r="D4" s="3">
+        <v>165</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
+      <c r="F4" s="8">
+        <v>105</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8">
+        <v>270</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8">
+        <v>400</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8">
+        <v>400</v>
+      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:30" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
+      <c r="C5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="D5" s="3">
+        <v>255</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="8">
+        <v>120</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8">
+        <v>375</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
+        <v>400</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8">
+        <v>400</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9" t="s">
+      <c r="C6" s="4">
+        <v>46147</v>
+      </c>
+      <c r="D6" s="3">
+        <v>500</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8">
+        <v>500</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
+        <v>400</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8">
+        <v>210</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8">
+        <v>610</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8">
+        <v>110</v>
+      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="T5" s="9" t="s">
+      <c r="C7" s="4">
+        <v>46175</v>
+      </c>
+      <c r="D7" s="3">
+        <v>425</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8">
+        <v>425</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8">
+        <v>400</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8">
+        <v>210</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8">
+        <v>610</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8">
+        <v>185</v>
+      </c>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V5" s="9" t="s">
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46205</v>
+      </c>
+      <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8">
+        <v>400</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8">
+        <v>400</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8">
+        <v>75</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8">
+        <v>475</v>
+      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8">
+        <v>75</v>
+      </c>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46235</v>
+      </c>
+      <c r="D9" s="3">
+        <v>450</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8">
+        <v>450</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8">
+        <v>400</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8">
+        <v>75</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8">
+        <v>475</v>
+      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4">
+        <v>46268</v>
+      </c>
+      <c r="D10" s="3">
+        <v>650</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="8">
+        <v>120</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8">
+        <v>770</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8">
+        <v>400</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8">
+        <v>435</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8">
+        <v>835</v>
+      </c>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4">
+        <v>46297</v>
+      </c>
+      <c r="D11" s="7">
+        <v>850</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
+        <v>150</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8">
+        <v>400</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8">
+        <v>535</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8">
+        <v>935</v>
+      </c>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8">
+        <v>-65</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="9" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="C12" s="4">
+        <v>46036</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="5">
+        <v>700</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11">
+        <v>700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
+        <v>720</v>
+      </c>
+      <c r="L12" s="8">
+        <v>263</v>
+      </c>
+      <c r="M12" s="8">
+        <v>526</v>
+      </c>
+      <c r="N12" s="8">
+        <v>963</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8">
+        <v>546</v>
+      </c>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4">
+        <v>46036</v>
+      </c>
+      <c r="D13" s="9">
+        <v>620</v>
+      </c>
+      <c r="E13" s="5">
+        <v>700</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="11">
+        <v>620</v>
+      </c>
+      <c r="I13" s="11">
+        <v>700</v>
+      </c>
+      <c r="J13" s="3">
+        <v>700</v>
+      </c>
+      <c r="K13" s="3">
+        <v>720</v>
+      </c>
+      <c r="L13" s="8">
+        <v>263</v>
+      </c>
+      <c r="M13" s="8">
+        <v>526</v>
+      </c>
+      <c r="N13" s="8">
+        <v>963</v>
+      </c>
+      <c r="O13" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P13" s="8">
+        <v>343</v>
+      </c>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="D14" s="9">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="11">
+        <v>500</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="3">
+        <v>700</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="8">
+        <v>263</v>
+      </c>
+      <c r="M14" s="8">
+        <v>526</v>
+      </c>
+      <c r="N14" s="8">
+        <v>963</v>
+      </c>
+      <c r="O14" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P14" s="8">
+        <v>463</v>
+      </c>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4">
+        <v>46084</v>
+      </c>
+      <c r="D15" s="9">
+        <v>350</v>
+      </c>
+      <c r="E15" s="3">
+        <v>450</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="11">
+        <v>350</v>
+      </c>
+      <c r="I15" s="11">
+        <v>450</v>
+      </c>
+      <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
+        <v>720</v>
+      </c>
+      <c r="L15" s="8">
+        <v>263</v>
+      </c>
+      <c r="M15" s="8">
+        <v>526</v>
+      </c>
+      <c r="N15" s="8">
+        <v>963</v>
+      </c>
+      <c r="O15" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8">
+        <v>796</v>
+      </c>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4">
+        <v>46106</v>
+      </c>
+      <c r="D16" s="9">
+        <v>550</v>
+      </c>
+      <c r="E16" s="3">
+        <v>600</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="11">
+        <v>550</v>
+      </c>
+      <c r="I16" s="11">
+        <v>600</v>
+      </c>
+      <c r="J16" s="3">
+        <v>700</v>
+      </c>
+      <c r="K16" s="3">
+        <v>720</v>
+      </c>
+      <c r="L16" s="8">
+        <v>263</v>
+      </c>
+      <c r="M16" s="8">
+        <v>526</v>
+      </c>
+      <c r="N16" s="8">
+        <v>963</v>
+      </c>
+      <c r="O16" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8">
+        <v>646</v>
+      </c>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="4">
+        <v>46112</v>
+      </c>
+      <c r="D17" s="9">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>800</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="11">
+        <v>700</v>
+      </c>
+      <c r="I17" s="11">
+        <v>800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>700</v>
+      </c>
+      <c r="K17" s="3">
+        <v>720</v>
+      </c>
+      <c r="L17" s="8">
+        <v>263</v>
+      </c>
+      <c r="M17" s="8">
+        <v>526</v>
+      </c>
+      <c r="N17" s="8">
+        <v>963</v>
+      </c>
+      <c r="O17" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P17" s="8">
+        <v>263</v>
+      </c>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4">
+        <v>46131</v>
+      </c>
+      <c r="D18" s="9">
+        <v>750</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="11">
+        <v>750</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="3">
+        <v>700</v>
+      </c>
+      <c r="K18" s="3">
+        <v>720</v>
+      </c>
+      <c r="L18" s="8">
+        <v>263</v>
+      </c>
+      <c r="M18" s="8">
+        <v>526</v>
+      </c>
+      <c r="N18" s="8">
+        <v>963</v>
+      </c>
+      <c r="O18" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P18" s="8">
+        <v>213</v>
+      </c>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11">
+        <v>1100</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3">
+        <v>720</v>
+      </c>
+      <c r="L19" s="8">
+        <v>263</v>
+      </c>
+      <c r="M19" s="8">
+        <v>526</v>
+      </c>
+      <c r="N19" s="8">
+        <v>963</v>
+      </c>
+      <c r="O19" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8">
+        <v>146</v>
+      </c>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y5" s="11" t="s">
+      <c r="C20" s="4">
+        <v>46150</v>
+      </c>
+      <c r="D20" s="9">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="3">
+        <v>700</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="8">
+        <v>325</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8">
+        <v>1025</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>25</v>
+      </c>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB5" s="9" t="s">
+      <c r="C21" s="4">
+        <v>46158</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10">
+        <v>850</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11">
+        <v>850</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3">
+        <v>720</v>
+      </c>
+      <c r="L21" s="8">
+        <v>263</v>
+      </c>
+      <c r="M21" s="8">
+        <v>526</v>
+      </c>
+      <c r="N21" s="8">
+        <v>963</v>
+      </c>
+      <c r="O21" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8">
+        <v>396</v>
+      </c>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="AC5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD5" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="C22" s="4">
+        <v>46189</v>
+      </c>
+      <c r="D22" s="9">
+        <v>950</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1050</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="11">
+        <v>950</v>
+      </c>
+      <c r="I22" s="11">
+        <v>1050</v>
+      </c>
+      <c r="J22" s="3">
+        <v>700</v>
+      </c>
+      <c r="K22" s="3">
+        <v>720</v>
+      </c>
+      <c r="L22" s="8">
+        <v>263</v>
+      </c>
+      <c r="M22" s="8">
+        <v>526</v>
+      </c>
+      <c r="N22" s="8">
+        <v>963</v>
+      </c>
+      <c r="O22" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8">
+        <v>196</v>
+      </c>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
     </row>
-    <row r="6" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="15">
-        <v>46024</v>
-      </c>
-      <c r="D6" s="14">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="4">
+        <v>46205</v>
+      </c>
+      <c r="D23" s="9">
+        <v>700</v>
+      </c>
+      <c r="E23" s="10">
+        <v>800</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="11">
+        <v>700</v>
+      </c>
+      <c r="I23" s="11">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>720</v>
+      </c>
+      <c r="L23" s="8">
+        <v>263</v>
+      </c>
+      <c r="M23" s="8">
+        <v>526</v>
+      </c>
+      <c r="N23" s="8">
+        <v>963</v>
+      </c>
+      <c r="O23" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P23" s="8">
+        <v>263</v>
+      </c>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4">
+        <v>46218</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="8">
         <v>0</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17">
-        <v>265</v>
-      </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17">
-        <v>530</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17">
-        <v>105</v>
-      </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17">
-        <v>210</v>
-      </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17">
-        <v>105</v>
-      </c>
-      <c r="Q6" s="14">
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46218</v>
+      </c>
+      <c r="D25" s="9">
+        <v>500</v>
+      </c>
+      <c r="E25" s="10">
+        <v>600</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="11">
+        <v>500</v>
+      </c>
+      <c r="I25" s="11">
+        <v>600</v>
+      </c>
+      <c r="J25" s="3">
+        <v>700</v>
+      </c>
+      <c r="K25" s="3">
         <v>720</v>
       </c>
-      <c r="R6" s="14">
-        <v>0</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14">
-        <f>T6+V6</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="14">
-        <f>U6+W6</f>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="13" t="e">
-        <f>#REF!+T6+V6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="14" t="e">
-        <f>#REF!*D6-(H6+L6)*D6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC6" s="18">
-        <f>Q6*F6-(J6+N6)*F6</f>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="19" t="e">
-        <f>AC6+AB6</f>
-        <v>#REF!</v>
-      </c>
+      <c r="L25" s="8">
+        <v>263</v>
+      </c>
+      <c r="M25" s="8">
+        <v>526</v>
+      </c>
+      <c r="N25" s="8">
+        <v>963</v>
+      </c>
+      <c r="O25" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P25" s="8">
+        <v>463</v>
+      </c>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
     </row>
-    <row r="7" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="15">
-        <v>46055</v>
-      </c>
-      <c r="D7" s="14">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16">
-        <v>0</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="14">
-        <v>175</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14">
-        <v>350</v>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="14">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4">
+        <v>46241</v>
+      </c>
+      <c r="D26" s="9">
+        <v>600</v>
+      </c>
+      <c r="E26" s="10">
+        <v>700</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="11">
+        <v>600</v>
+      </c>
+      <c r="I26" s="11">
+        <v>700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>700</v>
+      </c>
+      <c r="K26" s="3">
         <v>720</v>
       </c>
-      <c r="R7" s="14">
-        <v>0</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14">
-        <f t="shared" ref="X7:Y15" si="0">T7+V7</f>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="13" t="e">
-        <f>#REF!+T7+V7</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="14" t="e">
-        <f>#REF!*D7-(H7)*D7</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC7" s="18">
-        <f>Q7*F7-(J7)*F7</f>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="19" t="e">
-        <f>AC7+AB7</f>
-        <v>#REF!</v>
-      </c>
+      <c r="L26" s="8">
+        <v>263</v>
+      </c>
+      <c r="M26" s="8">
+        <v>526</v>
+      </c>
+      <c r="N26" s="8">
+        <v>963</v>
+      </c>
+      <c r="O26" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P26" s="8">
+        <v>363</v>
+      </c>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
     </row>
-    <row r="8" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="15">
-        <v>46084</v>
-      </c>
-      <c r="D8" s="14">
-        <v>1</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16">
-        <v>0</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="14">
-        <v>165</v>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14">
-        <v>330</v>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14">
-        <v>105</v>
-      </c>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14">
-        <v>210</v>
-      </c>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14">
-        <v>105</v>
-      </c>
-      <c r="Q8" s="14">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="4">
+        <v>46238</v>
+      </c>
+      <c r="D27" s="9">
+        <v>600</v>
+      </c>
+      <c r="E27" s="10">
+        <v>700</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="11">
+        <v>600</v>
+      </c>
+      <c r="I27" s="11">
+        <v>700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>700</v>
+      </c>
+      <c r="K27" s="3">
         <v>720</v>
       </c>
-      <c r="R8" s="14">
-        <v>0</v>
-      </c>
-      <c r="S8" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="13" t="e">
-        <f>#REF!+T8+V8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="14" t="e">
-        <f>#REF!*D8-(H8+L8)*D8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC8" s="18">
-        <f>Q8*F8-(J8)*F8</f>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="19" t="e">
-        <f>AC8+AB8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="L27" s="8">
+        <v>263</v>
+      </c>
+      <c r="M27" s="8">
+        <v>526</v>
+      </c>
+      <c r="N27" s="8">
+        <v>963</v>
+      </c>
+      <c r="O27" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8">
+        <v>546</v>
+      </c>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
     </row>
-    <row r="9" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="15">
-        <v>46114</v>
-      </c>
-      <c r="D9" s="14">
-        <v>1</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="14">
-        <v>255</v>
-      </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14">
-        <v>510</v>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14">
-        <v>120</v>
-      </c>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14">
-        <v>240</v>
-      </c>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14">
-        <v>120</v>
-      </c>
-      <c r="Q9" s="14">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4">
+        <v>46266</v>
+      </c>
+      <c r="D28" s="9">
+        <v>900</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="11">
+        <v>900</v>
+      </c>
+      <c r="I28" s="11">
+        <v>1000</v>
+      </c>
+      <c r="J28" s="3">
+        <v>700</v>
+      </c>
+      <c r="K28" s="3">
         <v>720</v>
       </c>
-      <c r="R9" s="14">
-        <v>0</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="13" t="e">
-        <f>#REF!+T9+V9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="14" t="e">
-        <f>#REF!*D9-(H9+L9)*D9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC9" s="18">
-        <f>Q9*F9-(J9)*F9</f>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="19" t="e">
-        <f t="shared" ref="AD9:AD15" si="1">AC9+AB9</f>
-        <v>#REF!</v>
-      </c>
+      <c r="L28" s="8">
+        <v>263</v>
+      </c>
+      <c r="M28" s="8">
+        <v>526</v>
+      </c>
+      <c r="N28" s="8">
+        <v>963</v>
+      </c>
+      <c r="O28" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P28" s="8">
+        <v>63</v>
+      </c>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
     </row>
-    <row r="10" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="15">
-        <v>46147</v>
-      </c>
-      <c r="D10" s="14">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16">
-        <v>0</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="14">
-        <v>500</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4">
+        <v>46273</v>
+      </c>
+      <c r="D29" s="9">
         <v>1000</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="14">
+      <c r="E29" s="10">
+        <v>1100</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I29" s="11">
+        <v>1100</v>
+      </c>
+      <c r="J29" s="3">
+        <v>700</v>
+      </c>
+      <c r="K29" s="3">
         <v>720</v>
       </c>
-      <c r="R10" s="14">
-        <v>0</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T10" s="20">
-        <v>135</v>
-      </c>
-      <c r="U10" s="21"/>
-      <c r="V10" s="20">
-        <v>75</v>
-      </c>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14">
-        <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-      <c r="Y10" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="13" t="e">
-        <f>#REF!+T10+V10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="14" t="e">
-        <f>Z10-H10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC10" s="18">
-        <f>Q10*F10-(J10)*F10</f>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
+      <c r="L29" s="8">
+        <v>263</v>
+      </c>
+      <c r="M29" s="8">
+        <v>526</v>
+      </c>
+      <c r="N29" s="8">
+        <v>963</v>
+      </c>
+      <c r="O29" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8">
+        <v>146</v>
+      </c>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
     </row>
-    <row r="11" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="23">
-        <v>46175</v>
-      </c>
-      <c r="D11" s="14">
-        <v>1</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="14">
-        <v>425</v>
-      </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14">
-        <v>825</v>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="14">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4">
+        <v>46288</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1050</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1200</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="11">
+        <v>1050</v>
+      </c>
+      <c r="I30" s="11">
+        <v>1200</v>
+      </c>
+      <c r="J30" s="3">
+        <v>700</v>
+      </c>
+      <c r="K30" s="3">
         <v>720</v>
       </c>
-      <c r="R11" s="14">
-        <v>0</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T11" s="20">
-        <v>135</v>
-      </c>
-      <c r="U11" s="21"/>
-      <c r="V11" s="20">
-        <v>75</v>
-      </c>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14">
-        <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-      <c r="Y11" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="13" t="e">
-        <f>#REF!+T11+V11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="14" t="e">
-        <f>Z11-H11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC11" s="18">
-        <f>Q11*F11-(J11)*F11</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
+      <c r="L30" s="8">
+        <v>263</v>
+      </c>
+      <c r="M30" s="8">
+        <v>526</v>
+      </c>
+      <c r="N30" s="8">
+        <v>963</v>
+      </c>
+      <c r="O30" s="8">
+        <v>1246</v>
+      </c>
+      <c r="P30" s="8">
+        <v>-87</v>
+      </c>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
     </row>
-    <row r="12" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="24">
-        <v>46205</v>
-      </c>
-      <c r="D12" s="14">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="14">
-        <v>400</v>
-      </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14">
-        <v>600</v>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="14">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="4">
+        <v>46292</v>
+      </c>
+      <c r="D31" s="9">
+        <v>1050</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1200</v>
+      </c>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="11">
+        <v>1050</v>
+      </c>
+      <c r="I31" s="11">
+        <v>1200</v>
+      </c>
+      <c r="J31" s="3">
+        <v>700</v>
+      </c>
+      <c r="K31" s="3">
         <v>720</v>
       </c>
-      <c r="R12" s="14">
-        <v>0</v>
-      </c>
-      <c r="S12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T12" s="20">
-        <v>75</v>
-      </c>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="Y12" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="13" t="e">
-        <f>#REF!+T12+V12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="14" t="e">
-        <f>Z12-H12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC12" s="18">
-        <f>Q12*F12-(J12)*F12</f>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="24">
-        <v>46235</v>
-      </c>
-      <c r="D13" s="14">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="14">
-        <v>450</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14">
-        <v>800</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>720</v>
-      </c>
-      <c r="R13" s="14">
-        <v>0</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T13" s="20">
-        <v>75</v>
-      </c>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="Y13" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="13" t="e">
-        <f>#REF!+T13+V13</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="14" t="e">
-        <f>Z13-H13</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC13" s="18">
-        <f>Q13*F13-(J13)*F13</f>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="24">
-        <v>46268</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="14">
-        <v>650</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14">
-        <v>1300</v>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14">
-        <v>120</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14">
-        <v>240</v>
-      </c>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14">
-        <v>120</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>720</v>
-      </c>
-      <c r="R14" s="14">
-        <v>0</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T14" s="25">
-        <v>135</v>
-      </c>
-      <c r="U14" s="14"/>
-      <c r="V14" s="25">
-        <v>300</v>
-      </c>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14">
-        <f t="shared" si="0"/>
-        <v>435</v>
-      </c>
-      <c r="Y14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="13" t="e">
-        <f>#REF!+T14+V14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="14" t="e">
-        <f>Z14-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC14" s="18">
-        <f>Q14*F14-(J14)*F14</f>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="24">
-        <v>46297</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="26">
-        <v>850</v>
-      </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26">
-        <v>1700</v>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26">
-        <v>150</v>
-      </c>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26">
-        <v>300</v>
-      </c>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26">
-        <v>150</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>720</v>
-      </c>
-      <c r="R15" s="14">
-        <v>0</v>
-      </c>
-      <c r="S15" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T15" s="25">
-        <v>135</v>
-      </c>
-      <c r="U15" s="14"/>
-      <c r="V15" s="26">
-        <v>400</v>
-      </c>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14">
-        <f t="shared" si="0"/>
-        <v>535</v>
-      </c>
-      <c r="Y15" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="13" t="e">
-        <f>#REF!+T15+V15</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="14" t="e">
-        <f>Z15-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC15" s="18">
-        <f>Q15*F15-(J15)*F15</f>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="P20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="15">
-        <v>46024</v>
-      </c>
-      <c r="D21" s="17">
-        <v>265</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="27">
-        <v>105</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27">
-        <v>370</v>
-      </c>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
-        <v>400</v>
-      </c>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27">
-        <v>0</v>
-      </c>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27">
-        <v>400</v>
-      </c>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="27"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="15">
-        <v>46055</v>
-      </c>
-      <c r="D22" s="14">
-        <v>175</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="27">
-        <v>0</v>
-      </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27">
-        <v>175</v>
-      </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27">
-        <v>400</v>
-      </c>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27">
-        <v>0</v>
-      </c>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27">
-        <v>400</v>
-      </c>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27">
-        <v>225</v>
-      </c>
-      <c r="Q22" s="27"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="15">
-        <v>46084</v>
-      </c>
-      <c r="D23" s="14">
-        <v>165</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="27">
-        <v>105</v>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27">
-        <v>270</v>
-      </c>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
-        <v>400</v>
-      </c>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27">
-        <v>0</v>
-      </c>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27">
-        <v>400</v>
-      </c>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27">
-        <v>130</v>
-      </c>
-      <c r="Q23" s="27"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="15">
-        <v>46114</v>
-      </c>
-      <c r="D24" s="14">
-        <v>255</v>
-      </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="27">
-        <v>120</v>
-      </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27">
-        <v>375</v>
-      </c>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27">
-        <v>400</v>
-      </c>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27">
-        <v>0</v>
-      </c>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27">
-        <v>400</v>
-      </c>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="27"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="15">
-        <v>46147</v>
-      </c>
-      <c r="D25" s="14">
-        <v>500</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="27">
-        <v>0</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27">
-        <v>500</v>
-      </c>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
-        <v>400</v>
-      </c>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27">
-        <v>210</v>
-      </c>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27">
-        <v>610</v>
-      </c>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27">
-        <v>110</v>
-      </c>
-      <c r="Q25" s="27"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="15">
-        <v>46175</v>
-      </c>
-      <c r="D26" s="14">
-        <v>425</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="27">
-        <v>0</v>
-      </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27">
-        <v>425</v>
-      </c>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27">
-        <v>400</v>
-      </c>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27">
-        <v>210</v>
-      </c>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27">
-        <v>610</v>
-      </c>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27">
-        <v>185</v>
-      </c>
-      <c r="Q26" s="27"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="15">
-        <v>46205</v>
-      </c>
-      <c r="D27" s="14">
-        <v>400</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="27">
-        <v>0</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27">
-        <v>400</v>
-      </c>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
-        <v>400</v>
-      </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27">
-        <v>75</v>
-      </c>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27">
-        <v>475</v>
-      </c>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27">
-        <v>75</v>
-      </c>
-      <c r="Q27" s="27"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="15">
-        <v>46235</v>
-      </c>
-      <c r="D28" s="14">
-        <v>450</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="27">
-        <v>0</v>
-      </c>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27">
-        <v>450</v>
-      </c>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27">
-        <v>400</v>
-      </c>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27">
-        <v>75</v>
-      </c>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27">
-        <v>475</v>
-      </c>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="27"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="15">
-        <v>46268</v>
-      </c>
-      <c r="D29" s="14">
-        <v>650</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="27">
-        <v>120</v>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27">
-        <v>770</v>
-      </c>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
-        <v>400</v>
-      </c>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27">
-        <v>435</v>
-      </c>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27">
-        <v>835</v>
-      </c>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27">
-        <v>65</v>
-      </c>
-      <c r="Q29" s="27"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="34">
-        <v>46297</v>
-      </c>
-      <c r="D30" s="35">
-        <v>850</v>
-      </c>
-      <c r="E30" s="35"/>
-      <c r="F30" s="36">
-        <v>150</v>
-      </c>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36">
-        <v>1000</v>
-      </c>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36">
-        <v>400</v>
-      </c>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36">
-        <v>535</v>
-      </c>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36">
-        <v>935</v>
-      </c>
-      <c r="O30" s="36"/>
-      <c r="P30" s="36">
-        <v>-65</v>
-      </c>
-      <c r="Q30" s="27"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="15">
-        <v>46036</v>
-      </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="17">
-        <v>700</v>
-      </c>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31">
-        <v>700</v>
-      </c>
-      <c r="J31" s="14">
-        <v>700</v>
-      </c>
-      <c r="K31" s="14">
-        <v>720</v>
-      </c>
-      <c r="L31" s="27">
+      <c r="L31" s="8">
         <v>263</v>
       </c>
-      <c r="M31" s="27">
+      <c r="M31" s="8">
         <v>526</v>
       </c>
-      <c r="N31" s="27">
+      <c r="N31" s="8">
         <v>963</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="8">
         <v>1246</v>
       </c>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="15">
-        <v>46036</v>
-      </c>
-      <c r="D32" s="28">
-        <v>620</v>
-      </c>
-      <c r="E32" s="17">
-        <v>700</v>
-      </c>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="31">
-        <v>620</v>
-      </c>
-      <c r="I32" s="31">
-        <v>700</v>
-      </c>
-      <c r="J32" s="14">
-        <v>700</v>
-      </c>
-      <c r="K32" s="14">
-        <v>720</v>
-      </c>
-      <c r="L32" s="27">
-        <v>263</v>
-      </c>
-      <c r="M32" s="27">
-        <v>526</v>
-      </c>
-      <c r="N32" s="27">
-        <v>963</v>
-      </c>
-      <c r="O32" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P32" s="27">
-        <v>343</v>
-      </c>
-      <c r="Q32" s="27"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="15">
-        <v>46054</v>
-      </c>
-      <c r="D33" s="28">
-        <v>500</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="31">
-        <v>500</v>
-      </c>
-      <c r="I33" s="31"/>
-      <c r="J33" s="14">
-        <v>700</v>
-      </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="27">
-        <v>263</v>
-      </c>
-      <c r="M33" s="27">
-        <v>526</v>
-      </c>
-      <c r="N33" s="27">
-        <v>963</v>
-      </c>
-      <c r="O33" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P33" s="27">
-        <v>463</v>
-      </c>
-      <c r="Q33" s="27"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="15">
-        <v>46084</v>
-      </c>
-      <c r="D34" s="28">
-        <v>350</v>
-      </c>
-      <c r="E34" s="14">
-        <v>450</v>
-      </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="31">
-        <v>350</v>
-      </c>
-      <c r="I34" s="31">
-        <v>450</v>
-      </c>
-      <c r="J34" s="14">
-        <v>700</v>
-      </c>
-      <c r="K34" s="14">
-        <v>720</v>
-      </c>
-      <c r="L34" s="27">
-        <v>263</v>
-      </c>
-      <c r="M34" s="27">
-        <v>526</v>
-      </c>
-      <c r="N34" s="27">
-        <v>963</v>
-      </c>
-      <c r="O34" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="15">
-        <v>46106</v>
-      </c>
-      <c r="D35" s="28">
-        <v>550</v>
-      </c>
-      <c r="E35" s="14">
-        <v>600</v>
-      </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="31">
-        <v>550</v>
-      </c>
-      <c r="I35" s="31">
-        <v>600</v>
-      </c>
-      <c r="J35" s="14">
-        <v>700</v>
-      </c>
-      <c r="K35" s="14">
-        <v>720</v>
-      </c>
-      <c r="L35" s="27">
-        <v>263</v>
-      </c>
-      <c r="M35" s="27">
-        <v>526</v>
-      </c>
-      <c r="N35" s="27">
-        <v>963</v>
-      </c>
-      <c r="O35" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="15">
-        <v>46112</v>
-      </c>
-      <c r="D36" s="28">
-        <v>700</v>
-      </c>
-      <c r="E36" s="14">
-        <v>800</v>
-      </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="31">
-        <v>700</v>
-      </c>
-      <c r="I36" s="31">
-        <v>800</v>
-      </c>
-      <c r="J36" s="14">
-        <v>700</v>
-      </c>
-      <c r="K36" s="14">
-        <v>720</v>
-      </c>
-      <c r="L36" s="27">
-        <v>263</v>
-      </c>
-      <c r="M36" s="27">
-        <v>526</v>
-      </c>
-      <c r="N36" s="27">
-        <v>963</v>
-      </c>
-      <c r="O36" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P36" s="27">
-        <v>263</v>
-      </c>
-      <c r="Q36" s="27"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="15">
-        <v>46131</v>
-      </c>
-      <c r="D37" s="28">
-        <v>750</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="31">
-        <v>750</v>
-      </c>
-      <c r="I37" s="31"/>
-      <c r="J37" s="14">
-        <v>700</v>
-      </c>
-      <c r="K37" s="14">
-        <v>720</v>
-      </c>
-      <c r="L37" s="27">
-        <v>263</v>
-      </c>
-      <c r="M37" s="27">
-        <v>526</v>
-      </c>
-      <c r="N37" s="27">
-        <v>963</v>
-      </c>
-      <c r="O37" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P37" s="27">
-        <v>213</v>
-      </c>
-      <c r="Q37" s="27"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="28"/>
-      <c r="E38" s="14">
-        <v>1100</v>
-      </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31">
-        <v>1100</v>
-      </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14">
-        <v>720</v>
-      </c>
-      <c r="L38" s="27">
-        <v>263</v>
-      </c>
-      <c r="M38" s="27">
-        <v>526</v>
-      </c>
-      <c r="N38" s="27">
-        <v>963</v>
-      </c>
-      <c r="O38" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="15">
-        <v>46150</v>
-      </c>
-      <c r="D39" s="28">
-        <v>1000</v>
-      </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="31">
-        <v>1000</v>
-      </c>
-      <c r="I39" s="31"/>
-      <c r="J39" s="14">
-        <v>700</v>
-      </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="27">
-        <v>325</v>
-      </c>
-      <c r="M39" s="27">
-        <v>0</v>
-      </c>
-      <c r="N39" s="27">
-        <v>1025</v>
-      </c>
-      <c r="O39" s="27">
-        <v>0</v>
-      </c>
-      <c r="P39" s="27">
-        <v>25</v>
-      </c>
-      <c r="Q39" s="27"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="15">
-        <v>46158</v>
-      </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="30">
-        <v>850</v>
-      </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31">
-        <v>850</v>
-      </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14">
-        <v>720</v>
-      </c>
-      <c r="L40" s="27">
-        <v>263</v>
-      </c>
-      <c r="M40" s="27">
-        <v>526</v>
-      </c>
-      <c r="N40" s="27">
-        <v>963</v>
-      </c>
-      <c r="O40" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="15">
-        <v>46189</v>
-      </c>
-      <c r="D41" s="28">
-        <v>950</v>
-      </c>
-      <c r="E41" s="30">
-        <v>1050</v>
-      </c>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="31">
-        <v>950</v>
-      </c>
-      <c r="I41" s="31">
-        <v>1050</v>
-      </c>
-      <c r="J41" s="14">
-        <v>700</v>
-      </c>
-      <c r="K41" s="14">
-        <v>720</v>
-      </c>
-      <c r="L41" s="27">
-        <v>263</v>
-      </c>
-      <c r="M41" s="27">
-        <v>526</v>
-      </c>
-      <c r="N41" s="27">
-        <v>963</v>
-      </c>
-      <c r="O41" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="15">
-        <v>46205</v>
-      </c>
-      <c r="D42" s="28">
-        <v>700</v>
-      </c>
-      <c r="E42" s="30">
-        <v>800</v>
-      </c>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="31">
-        <v>700</v>
-      </c>
-      <c r="I42" s="31">
-        <v>800</v>
-      </c>
-      <c r="J42" s="14">
-        <v>700</v>
-      </c>
-      <c r="K42" s="14">
-        <v>720</v>
-      </c>
-      <c r="L42" s="27">
-        <v>263</v>
-      </c>
-      <c r="M42" s="27">
-        <v>526</v>
-      </c>
-      <c r="N42" s="27">
-        <v>963</v>
-      </c>
-      <c r="O42" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P42" s="27">
-        <v>263</v>
-      </c>
-      <c r="Q42" s="27"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="15">
-        <v>46218</v>
-      </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="27">
-        <v>0</v>
-      </c>
-      <c r="M43" s="27">
-        <v>0</v>
-      </c>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="15">
-        <v>46218</v>
-      </c>
-      <c r="D44" s="28">
-        <v>500</v>
-      </c>
-      <c r="E44" s="30">
-        <v>600</v>
-      </c>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="31">
-        <v>500</v>
-      </c>
-      <c r="I44" s="31">
-        <v>600</v>
-      </c>
-      <c r="J44" s="14">
-        <v>700</v>
-      </c>
-      <c r="K44" s="14">
-        <v>720</v>
-      </c>
-      <c r="L44" s="27">
-        <v>263</v>
-      </c>
-      <c r="M44" s="27">
-        <v>526</v>
-      </c>
-      <c r="N44" s="27">
-        <v>963</v>
-      </c>
-      <c r="O44" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P44" s="27">
-        <v>463</v>
-      </c>
-      <c r="Q44" s="27"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="15">
-        <v>46241</v>
-      </c>
-      <c r="D45" s="28">
-        <v>600</v>
-      </c>
-      <c r="E45" s="30">
-        <v>700</v>
-      </c>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="31">
-        <v>600</v>
-      </c>
-      <c r="I45" s="31">
-        <v>700</v>
-      </c>
-      <c r="J45" s="14">
-        <v>700</v>
-      </c>
-      <c r="K45" s="14">
-        <v>720</v>
-      </c>
-      <c r="L45" s="27">
-        <v>263</v>
-      </c>
-      <c r="M45" s="27">
-        <v>526</v>
-      </c>
-      <c r="N45" s="27">
-        <v>963</v>
-      </c>
-      <c r="O45" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P45" s="27">
-        <v>363</v>
-      </c>
-      <c r="Q45" s="27"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="15">
-        <v>46238</v>
-      </c>
-      <c r="D46" s="28">
-        <v>600</v>
-      </c>
-      <c r="E46" s="30">
-        <v>700</v>
-      </c>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="31">
-        <v>600</v>
-      </c>
-      <c r="I46" s="31">
-        <v>700</v>
-      </c>
-      <c r="J46" s="14">
-        <v>700</v>
-      </c>
-      <c r="K46" s="14">
-        <v>720</v>
-      </c>
-      <c r="L46" s="27">
-        <v>263</v>
-      </c>
-      <c r="M46" s="27">
-        <v>526</v>
-      </c>
-      <c r="N46" s="27">
-        <v>963</v>
-      </c>
-      <c r="O46" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="15">
-        <v>46266</v>
-      </c>
-      <c r="D47" s="28">
-        <v>900</v>
-      </c>
-      <c r="E47" s="30">
-        <v>1000</v>
-      </c>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="31">
-        <v>900</v>
-      </c>
-      <c r="I47" s="31">
-        <v>1000</v>
-      </c>
-      <c r="J47" s="14">
-        <v>700</v>
-      </c>
-      <c r="K47" s="14">
-        <v>720</v>
-      </c>
-      <c r="L47" s="27">
-        <v>263</v>
-      </c>
-      <c r="M47" s="27">
-        <v>526</v>
-      </c>
-      <c r="N47" s="27">
-        <v>963</v>
-      </c>
-      <c r="O47" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P47" s="27">
-        <v>63</v>
-      </c>
-      <c r="Q47" s="27"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="15">
-        <v>46273</v>
-      </c>
-      <c r="D48" s="28">
-        <v>1000</v>
-      </c>
-      <c r="E48" s="30">
-        <v>1100</v>
-      </c>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="31">
-        <v>1000</v>
-      </c>
-      <c r="I48" s="31">
-        <v>1100</v>
-      </c>
-      <c r="J48" s="14">
-        <v>700</v>
-      </c>
-      <c r="K48" s="14">
-        <v>720</v>
-      </c>
-      <c r="L48" s="27">
-        <v>263</v>
-      </c>
-      <c r="M48" s="27">
-        <v>526</v>
-      </c>
-      <c r="N48" s="27">
-        <v>963</v>
-      </c>
-      <c r="O48" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="15">
-        <v>46288</v>
-      </c>
-      <c r="D49" s="28">
-        <v>1050</v>
-      </c>
-      <c r="E49" s="30">
-        <v>1200</v>
-      </c>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="31">
-        <v>1050</v>
-      </c>
-      <c r="I49" s="31">
-        <v>1200</v>
-      </c>
-      <c r="J49" s="14">
-        <v>700</v>
-      </c>
-      <c r="K49" s="14">
-        <v>720</v>
-      </c>
-      <c r="L49" s="27">
-        <v>263</v>
-      </c>
-      <c r="M49" s="27">
-        <v>526</v>
-      </c>
-      <c r="N49" s="27">
-        <v>963</v>
-      </c>
-      <c r="O49" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P49" s="27">
-        <v>-87</v>
-      </c>
-      <c r="Q49" s="27"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="15">
-        <v>46292</v>
-      </c>
-      <c r="D50" s="28">
-        <v>1050</v>
-      </c>
-      <c r="E50" s="30">
-        <v>1200</v>
-      </c>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="31">
-        <v>1050</v>
-      </c>
-      <c r="I50" s="31">
-        <v>1200</v>
-      </c>
-      <c r="J50" s="14">
-        <v>700</v>
-      </c>
-      <c r="K50" s="14">
-        <v>720</v>
-      </c>
-      <c r="L50" s="27">
-        <v>263</v>
-      </c>
-      <c r="M50" s="27">
-        <v>526</v>
-      </c>
-      <c r="N50" s="27">
-        <v>963</v>
-      </c>
-      <c r="O50" s="27">
-        <v>1246</v>
-      </c>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27">
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8">
         <v>46</v>
       </c>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="H4:P4"/>
-    <mergeCell ref="Q4:AA4"/>
-    <mergeCell ref="AB4:AD4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/O.F China lane Analysis.xlsx
+++ b/O.F China lane Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/thuhuong_ngo_nykgroup_com/Documents/Streamlit_Starter_Kit_CS_HAD/2026 bidding preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{3F479565-A40F-41CD-8273-DAD36C479CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DE00E3-5877-4015-BFA1-7898D73475B0}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{3F479565-A40F-41CD-8273-DAD36C479CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0705E04F-B5B7-4345-90FB-A0BCFD3E08C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{110F69CB-7609-4F85-B310-6E083916393A}"/>
   </bookViews>
@@ -15748,7 +15748,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Carrier</t>
   </si>
@@ -15802,9 +15802,6 @@
   </si>
   <si>
     <t>PAN OCEAN</t>
-  </si>
-  <si>
-    <t>4/27/2026&gt;&gt;5/5</t>
   </si>
   <si>
     <t>OF BR 40'</t>
@@ -15935,7 +15932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -15969,9 +15966,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16335,58 +16329,58 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -17186,8 +17180,8 @@
       <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>18</v>
+      <c r="C19" s="4">
+        <v>46139</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="3">
